--- a/output/pdf_financials_xlsx/CZZ.xlsx
+++ b/output/pdf_financials_xlsx/CZZ.xlsx
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.15789</v>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.15789</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.15789</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.15789</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.15789</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -26229,10 +26229,10 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>0.105076</v>
+        <v>-0.105076</v>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.15789</v>
+        <v>-0.15789</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CZZ.xlsx
+++ b/output/pdf_financials_xlsx/CZZ.xlsx
@@ -940,18 +940,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.000611</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2e-06</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000376</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1803,7 +1799,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.105076</v>
+        <v>-0.1047</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.15789</v>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.105076</v>
+        <v>-0.1047</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.15789</v>
@@ -2140,16 +2136,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.056256</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.768259</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.293737</v>
@@ -2161,22 +2157,22 @@
         <v>0.294509</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.228297</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.122614</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.026243</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.137391</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.170563</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="35">
@@ -2232,16 +2228,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.056256</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.768259</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.293737</v>
@@ -2253,22 +2249,22 @@
         <v>0.294509</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.228297</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.122614</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.026243</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.137391</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.170563</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="37">
@@ -2790,10 +2786,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.125588</v>
+        <v>0.069332</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.7785069999999999</v>
+        <v>0.010248</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.012785</v>
@@ -2805,10 +2801,10 @@
         <v>0.010302</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.238799</v>
+        <v>0.010502</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.133409</v>
+        <v>0.010795</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -7139,7 +7135,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10323,7 +10319,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -11447,7 +11443,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11777,7 +11773,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -25330,7 +25326,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -26049,7 +26045,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -26699,7 +26695,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
@@ -26782,7 +26778,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">

--- a/output/pdf_financials_xlsx/CZZ.xlsx
+++ b/output/pdf_financials_xlsx/CZZ.xlsx
@@ -590,15 +590,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -690,30 +686,26 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.000135</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.000208</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.020964</v>
+        <v>0.021678</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.042188</v>
+        <v>0.043721</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.048239</v>
+        <v>0.050408</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.033065</v>
+        <v>0.040006</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.041835</v>
+        <v>0.049121</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.038164</v>
@@ -740,15 +732,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -790,15 +778,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -840,30 +824,26 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.000135</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.000208</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.020964</v>
+        <v>0.021678</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.042188</v>
+        <v>0.043721</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.048239</v>
+        <v>0.050408</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.033065</v>
+        <v>0.040006</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.041835</v>
+        <v>0.049121</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.038164</v>
@@ -913,7 +893,7 @@
         <v>-0.091215</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.041835</v>
+        <v>-0.049121</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.038164</v>
@@ -986,15 +966,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1036,15 +1012,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1086,15 +1058,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1186,15 +1154,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1430,15 +1394,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1480,15 +1440,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -14873,7 +14829,11 @@
           <t>Issuance of units under a private placement 8</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -15768,7 +15728,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -22513,7 +22477,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E198" s="5" t="n">
         <v>0.000135</v>
       </c>
